--- a/validation/insurance_conditions_test_case_list.xlsx
+++ b/validation/insurance_conditions_test_case_list.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1307,6 +1307,78 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sc23</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Issue #2040: one location under a single condition covered by three policy-layers; two share condition terms and one differs. Reproduces account-row-order dependence of loss_il (order-dependent before the cond-all layer-preservation fix).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sc24</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Edge case: three co-insurance policy-layers on one condition with identical condition terms, differing only in LayerParticipation. Layers collapse harmlessly; guards that the fix stays a no-op when all layers share a profile.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/validation/insurance_conditions_test_case_list.xlsx
+++ b/validation/insurance_conditions_test_case_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1379,6 +1379,42 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sc25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Three nested conditions on one policy where a cond tag is innermost on one location and nested inside another tag on a second location (A p2 with B p3 on loc 10; C p1 with A p2 on loc 11). Covers conditions that must nest being kept on separate FM levels, and levels being applied innermost-first.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/validation/insurance_conditions_test_case_list.xlsx
+++ b/validation/insurance_conditions_test_case_list.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1415,6 +1415,42 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sc26</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Five nested conditions on one location with the account rows written deepest-first (priority 5 down to 1). Covers cond FM levels being applied innermost-first regardless of account-file order: reversed, the inner 30,000 deductible and outer 60,000 limit swap and the loss halves.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/validation/insurance_conditions_test_case_list.xlsx
+++ b/validation/insurance_conditions_test_case_list.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1379,6 +1379,78 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sc25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Three nested conditions on one policy where a cond tag is innermost on one location and nested inside another tag on a second location (A p2 with B p3 on loc 10; C p1 with A p2 on loc 11). Covers conditions that must nest being kept on separate FM levels, and levels being applied innermost-first.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sc26</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Five nested conditions on one location with the account rows written deepest-first (priority 5 down to 1). Covers cond FM levels being applied innermost-first regardless of account-file order: reversed, the inner 30,000 deductible and outer 60,000 limit swap and the loss halves.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
